--- a/output/pdf_financials_xlsx/SKUL.xlsx
+++ b/output/pdf_financials_xlsx/SKUL.xlsx
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.279032</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.573032</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.519002</v>
       </c>
     </row>
     <row r="93">
@@ -3057,7 +3057,11 @@
           <t>Reserves 8,9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3305,7 +3309,11 @@
           <t>Reserves 8,9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.279032</v>
       </c>

--- a/output/pdf_financials_xlsx/SKUL.xlsx
+++ b/output/pdf_financials_xlsx/SKUL.xlsx
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.288574</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.065675</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006603</v>
       </c>
     </row>
     <row r="35">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.288574</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.065675</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.006603</v>
       </c>
     </row>
     <row r="37">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.373905</v>
+        <v>0.085331</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.133175</v>
+        <v>0.0675</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007603</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="49">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/SKUL.xlsx
+++ b/output/pdf_financials_xlsx/SKUL.xlsx
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.024739</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.105239</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.142876</v>
       </c>
     </row>
     <row r="65">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.044739</v>
+        <v>0.069478</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.130739</v>
+        <v>0.235978</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.189376</v>
+        <v>0.332252</v>
       </c>
     </row>
     <row r="69">
